--- a/data/trans_camb/P6907S1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 13,93</t>
+          <t>-15,12; 11,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 4,8</t>
+          <t>-14,98; 5,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 6,34</t>
+          <t>-16,15; 6,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 0,0</t>
+          <t>-19,0; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 12,99</t>
+          <t>-8,69; 12,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 21,98</t>
+          <t>-5,87; 20,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 5,45</t>
+          <t>-11,07; 4,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 6,53</t>
+          <t>-8,63; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 8,82</t>
+          <t>-8,88; 7,73</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,74</t>
+          <t>-100,0; 235,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 337,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,03; 253,55</t>
+          <t>-81,05; 256,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,0; 452,51</t>
+          <t>-88,35; 287,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 8,71</t>
+          <t>-13,8; 7,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 2,76</t>
+          <t>-15,75; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 14,04</t>
+          <t>-10,09; 15,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 19,69</t>
+          <t>-9,13; 22,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 0,0</t>
+          <t>-18,46; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 7,38</t>
+          <t>-12,21; 7,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 6,41</t>
+          <t>-10,36; 6,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 0,52</t>
+          <t>-13,17; 0,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 7,73</t>
+          <t>-9,64; 6,98</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 169,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 496,9</t>
+          <t>-100,0; 580,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 88,08</t>
+          <t>-100,0; 74,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 268,36</t>
+          <t>-80,4; 217,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 26,69</t>
+          <t>-15,37; 28,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 7,06</t>
+          <t>-18,75; 7,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 15,52</t>
+          <t>-12,38; 15,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 0,0</t>
+          <t>-27,43; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 16,58</t>
+          <t>-18,38; 16,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 20,29</t>
+          <t>-9,22; 20,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 15,16</t>
+          <t>-14,15; 13,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 5,21</t>
+          <t>-14,99; 4,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 15,42</t>
+          <t>-4,6; 14,82</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 395,25</t>
+          <t>-65,3; 403,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,76; —</t>
+          <t>-50,7; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 561,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 199,11</t>
+          <t>-100,0; 224,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 351,64</t>
+          <t>-30,7; 338,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 42,61</t>
+          <t>-9,44; 39,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 4,26</t>
+          <t>-12,28; 4,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 31,26</t>
+          <t>-6,99; 26,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 45,08</t>
+          <t>-15,82; 43,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 0,0</t>
+          <t>-26,21; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 0,87</t>
+          <t>-28,29; 0,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 27,36</t>
+          <t>-8,29; 25,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -0,54</t>
+          <t>-13,6; -0,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 7,1</t>
+          <t>-11,84; 5,67</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 1148,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 948,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 251,86</t>
+          <t>-100,0; 242,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 45,4</t>
+          <t>-16,36; 41,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,67; -3,77</t>
+          <t>-30,92; -3,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 1,72</t>
+          <t>-30,38; 1,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-71,51; 0,0</t>
+          <t>-71,08; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 0,0</t>
+          <t>-71,38; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-71,79; 0,0</t>
+          <t>-72,01; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 16,79</t>
+          <t>-23,41; 16,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -6,02</t>
+          <t>-31,74; -5,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-31,11; -3,02</t>
+          <t>-30,43; -3,35</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 355,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-29,07; -4,86</t>
+          <t>-29,3; -5,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 11,41</t>
+          <t>-21,88; 10,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 30,73</t>
+          <t>-7,83; 29,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 0,0</t>
+          <t>-36,29; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 0,0</t>
+          <t>-36,29; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 7,83</t>
+          <t>-25,65; 8,02</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -3,72</t>
+          <t>-23,94; -5,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 7,53</t>
+          <t>-18,78; 7,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 15,02</t>
+          <t>-10,23; 14,87</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 266,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 487,02</t>
+          <t>-42,67; 560,88</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 161,69</t>
+          <t>-100,0; 237,38</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 278,24</t>
+          <t>-55,07; 262,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -6,16</t>
+          <t>-22,42; -5,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-18,81; -1,4</t>
+          <t>-19,14; -1,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 14,74</t>
+          <t>-8,91; 15,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 0,34</t>
+          <t>-23,98; 0,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 0,32</t>
+          <t>-23,91; -0,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 17,93</t>
+          <t>-10,18; 18,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -4,52</t>
+          <t>-18,11; -4,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-17,63; -3,72</t>
+          <t>-16,91; -2,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 12,79</t>
+          <t>-4,92; 13,42</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,19</t>
+          <t>-100,0; 42,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 213,89</t>
+          <t>-55,4; 211,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2099,27 +2099,27 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 66,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 286,78</t>
+          <t>-48,55; 279,49</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,02</t>
+          <t>-100,0; 1,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-94,19; -32,11</t>
+          <t>-93,83; -17,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 142,25</t>
+          <t>-29,58; 161,16</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 23,29</t>
+          <t>-6,22; 21,53</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -2,39</t>
+          <t>-10,95; -2,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,79; -2,45</t>
+          <t>-11,21; -2,46</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-26,46; -6,35</t>
+          <t>-26,81; -6,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-26,99; -6,24</t>
+          <t>-26,41; -6,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-23,66; -1,07</t>
+          <t>-24,86; -1,01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 9,58</t>
+          <t>-9,86; 8,66</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -5,07</t>
+          <t>-14,37; -5,02</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,23; -2,47</t>
+          <t>-12,88; -2,64</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 662,25</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 20,77</t>
+          <t>-100,0; 93,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,82</t>
+          <t>-100,0; 152,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,72</t>
+          <t>-100,0; -13,74</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,05</t>
+          <t>-8,15; 1,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -2,52</t>
+          <t>-9,37; -2,5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,02</t>
+          <t>-2,54; 6,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -2,21</t>
+          <t>-13,33; -2,67</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -3,75</t>
+          <t>-13,36; -4,09</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,75</t>
+          <t>-7,6; 2,37</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -1,63</t>
+          <t>-8,81; -1,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -4,08</t>
+          <t>-9,4; -4,12</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,34</t>
+          <t>-3,55; 3,33</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 20,46</t>
+          <t>-75,87; 17,28</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-80,42; -29,97</t>
+          <t>-82,47; -29,69</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 106,95</t>
+          <t>-23,83; 92,94</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-92,52; -9,92</t>
+          <t>-100,0; -19,6</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-93,29; -43,66</t>
+          <t>-93,2; -45,35</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 35,67</t>
+          <t>-54,89; 31,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -15,37</t>
+          <t>-77,5; -14,71</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-81,76; -47,87</t>
+          <t>-81,84; -44,51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 39,87</t>
+          <t>-31,26; 45,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6907S1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-5,47</t>
+          <t>-5,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>7,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 11,8</t>
+          <t>-13,77; 14,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 5,84</t>
+          <t>-15,15; 6,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 6,25</t>
+          <t>-16,49; 5,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 0,0</t>
+          <t>-15,69; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 12,04</t>
+          <t>-7,86; 13,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 20,48</t>
+          <t>-4,18; 22,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 4,48</t>
+          <t>-11,26; 6,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 5,83</t>
+          <t>-9,0; 6,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 7,73</t>
+          <t>-8,81; 8,01</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-61,02%</t>
+          <t>-65,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>148,84%</t>
+          <t>197,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-15,62%</t>
+          <t>-10,05%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 235,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 337,54</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,05; 256,73</t>
+          <t>-82,41; 288,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,35; 287,98</t>
+          <t>-84,99; 351,69</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 7,71</t>
+          <t>-15,12; 7,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 2,5</t>
+          <t>-14,71; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 15,77</t>
+          <t>-12,1; 12,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 22,51</t>
+          <t>-11,71; 19,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 0,0</t>
+          <t>-18,25; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 7,6</t>
+          <t>-13,76; 6,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 6,75</t>
+          <t>-10,68; 6,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 0,43</t>
+          <t>-12,63; 0,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,98</t>
+          <t>-8,13; 7,53</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-15,59%</t>
+          <t>-18,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-6,53%</t>
+          <t>-11,09%</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 580,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 257,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,52</t>
+          <t>-100,0; 49,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 217,38</t>
+          <t>-73,75; 241,96</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>5,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 28,56</t>
+          <t>-14,91; 28,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 7,73</t>
+          <t>-19,35; 5,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 15,46</t>
+          <t>-11,09; 16,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 0,0</t>
+          <t>-27,67; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 16,81</t>
+          <t>-18,42; 19,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 20,99</t>
+          <t>-10,25; 20,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 13,39</t>
+          <t>-13,68; 14,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 4,99</t>
+          <t>-15,13; 4,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 14,82</t>
+          <t>-6,25; 14,11</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 403,62</t>
+          <t>-63,11; 455,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,7; —</t>
+          <t>-62,76; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 561,48</t>
+          <t>-100,0; 847,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,75</t>
+          <t>-100,0; 212,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 338,75</t>
+          <t>-35,95; 344,15</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-7,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-1,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 39,63</t>
+          <t>-8,7; 39,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 4,22</t>
+          <t>-12,89; 4,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 26,45</t>
+          <t>-7,89; 25,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 43,61</t>
+          <t>-15,15; 47,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 0,0</t>
+          <t>-27,59; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 0,93</t>
+          <t>-27,82; 1,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 25,96</t>
+          <t>-7,15; 32,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -0,5</t>
+          <t>-13,39; -0,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 5,67</t>
+          <t>-9,08; 10,59</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-89,38%</t>
+          <t>-82,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-40,24%</t>
+          <t>-22,79%</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1148,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 948,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 242,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,41</t>
+          <t>-9,66</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-14,32</t>
+          <t>-14,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 41,15</t>
+          <t>-15,72; 40,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-30,92; -3,75</t>
+          <t>-30,8; -3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 1,88</t>
+          <t>-28,25; 1,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 0,0</t>
+          <t>-71,99; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 0,0</t>
+          <t>-72,0; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-72,01; 0,0</t>
+          <t>-71,77; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 16,57</t>
+          <t>-22,95; 15,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,74; -5,88</t>
+          <t>-33,66; -6,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-30,43; -3,35</t>
+          <t>-32,23; -3,06</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-76,24%</t>
+          <t>-78,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-88,77%</t>
+          <t>-89,79%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 355,17</t>
+          <t>-100,0; 368,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11,22</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-29,3; -5,08</t>
+          <t>-29,98; -5,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 10,99</t>
+          <t>-21,55; 11,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 29,76</t>
+          <t>-8,55; 26,43</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 0,0</t>
+          <t>-37,61; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 0,0</t>
+          <t>-37,61; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 8,02</t>
+          <t>-21,46; 8,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-23,94; -5,46</t>
+          <t>-24,57; -5,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 7,59</t>
+          <t>-18,96; 7,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 14,87</t>
+          <t>-11,78; 13,35</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-20,26%</t>
+          <t>-22,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 560,88</t>
+          <t>-46,15; 468,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 237,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 262,03</t>
+          <t>-60,11; 219,69</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,7</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-22,42; -5,93</t>
+          <t>-20,9; -6,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -1,4</t>
+          <t>-18,78; -1,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 15,08</t>
+          <t>-7,99; 15,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 0,17</t>
+          <t>-24,59; 0,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -0,73</t>
+          <t>-24,1; -0,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 18,23</t>
+          <t>-8,4; 17,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-18,11; -4,36</t>
+          <t>-18,26; -4,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-16,91; -2,84</t>
+          <t>-17,95; -3,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 13,42</t>
+          <t>-4,34; 13,41</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,62</t>
+          <t>-100,0; 35,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 211,63</t>
+          <t>-48,34; 239,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2099,27 +2099,27 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,27</t>
+          <t>-100,0; 66,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 279,49</t>
+          <t>-43,95; 324,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,53</t>
+          <t>-100,0; -24,0</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-93,83; -17,51</t>
+          <t>-94,2; -22,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 161,16</t>
+          <t>-27,86; 153,97</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-11,67</t>
+          <t>-11,39</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-7,16</t>
+          <t>-7,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 21,53</t>
+          <t>-5,24; 21,71</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -2,49</t>
+          <t>-10,63; -2,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -2,46</t>
+          <t>-11,23; -2,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-26,81; -6,48</t>
+          <t>-28,32; -6,35</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-26,41; -6,14</t>
+          <t>-27,0; -6,41</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-24,86; -1,01</t>
+          <t>-24,07; -1,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 8,66</t>
+          <t>-10,04; 9,42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -5,02</t>
+          <t>-13,84; -5,01</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -2,64</t>
+          <t>-13,1; -3,0</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-78,67%</t>
+          <t>-76,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-82,17%</t>
+          <t>-81,67%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 662,25</t>
+          <t>-100,0; 658,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,75</t>
+          <t>-100,0; 62,16</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,05</t>
+          <t>-100,0; 147,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,74</t>
+          <t>-100,0; -8,21</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,01</t>
+          <t>-8,19; 1,67</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -2,5</t>
+          <t>-9,23; -2,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,79</t>
+          <t>-3,06; 6,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,67</t>
+          <t>-12,88; -2,73</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -4,09</t>
+          <t>-13,14; -3,94</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,37</t>
+          <t>-6,69; 3,61</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -1,36</t>
+          <t>-8,22; -1,61</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -4,12</t>
+          <t>-9,66; -4,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,33</t>
+          <t>-3,55; 3,13</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-24,15%</t>
+          <t>-14,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-2,45%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 17,28</t>
+          <t>-74,98; 30,74</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -29,69</t>
+          <t>-81,96; -27,42</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 92,94</t>
+          <t>-29,31; 88,61</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,6</t>
+          <t>-93,37; -20,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-93,2; -45,35</t>
+          <t>-92,99; -43,82</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 31,19</t>
+          <t>-47,2; 56,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-77,5; -14,71</t>
+          <t>-76,33; -17,21</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-81,84; -44,51</t>
+          <t>-81,41; -46,05</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 45,57</t>
+          <t>-31,36; 37,43</t>
         </is>
       </c>
     </row>
